--- a/artfynd/S 3008-2025 artfynd.xlsx
+++ b/artfynd/S 3008-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AZ80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123498</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123522</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123478</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123485</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123486</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123480</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123515</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123488</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112409</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115608</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116791</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116937</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117056</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2675,6 +2770,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117273</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123494</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2869,6 +2974,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123495</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2991,6 +3101,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3128,6 +3243,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114741</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3225,6 +3345,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123520</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3322,6 +3447,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123521</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123483</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3516,6 +3651,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123499</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123500</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3710,6 +3855,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123501</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3807,6 +3957,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123496</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3954,6 +4109,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4103,6 +4263,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114328</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123489</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123490</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123491</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4519,6 +4699,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123516</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4621,6 +4806,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123493</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4757,6 +4947,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113196</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4883,6 +5078,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129113282</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5015,6 +5215,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114612</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5151,6 +5356,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114882</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5287,6 +5497,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115520</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5389,6 +5604,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123481</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5491,6 +5711,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123482</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5593,6 +5818,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123502</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5690,6 +5920,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123503</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5787,6 +6022,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123504</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5884,6 +6124,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123505</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5986,6 +6231,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123506</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6088,6 +6338,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123507</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6190,6 +6445,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123508</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6287,6 +6547,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123509</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6389,6 +6654,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123510</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6486,6 +6756,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123511</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6583,6 +6858,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123512</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6680,6 +6960,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123513</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6782,6 +7067,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123514</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6889,6 +7179,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112541</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6996,6 +7291,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112558</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7103,6 +7403,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112589</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7210,6 +7515,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112623</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7317,6 +7627,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112874</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7434,6 +7749,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7556,6 +7876,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118114</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7653,6 +7978,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129123484</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7789,6 +8119,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115715</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7916,6 +8251,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116487</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8033,6 +8373,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116916</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8140,6 +8485,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112360</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8247,6 +8597,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112486</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8354,6 +8709,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112584</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8461,6 +8821,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129112851</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8583,6 +8948,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115554</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8700,6 +9070,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116888</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8817,6 +9192,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116986</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8934,6 +9314,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117538</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9051,6 +9436,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117890</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9168,6 +9558,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129118014</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9285,8 +9680,94 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129117456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>